--- a/excel/output_stats_sfvv/durbin/DVSInsertionData.xlsx
+++ b/excel/output_stats_sfvv/durbin/DVSInsertionData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,21 @@
           <t>voltage_level</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>voltage_value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>frequency_ghz</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>performance_level</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -451,13 +466,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>kernel_durbin</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -467,13 +491,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>polybench_alloc_data</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -483,13 +516,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>polybench_alloc_data</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -499,13 +541,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>print_array</t>
+          <t>polybench_alloc_data</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -515,13 +566,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>print_array</t>
+          <t>polybench_alloc_data</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -531,13 +591,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>print_array</t>
+          <t>polybench_alloc_data</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -551,9 +620,18 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -567,9 +645,18 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -583,9 +670,18 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -595,13 +691,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kernel_durbin</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -615,9 +720,18 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -631,9 +745,18 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -647,9 +770,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -659,13 +791,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>polybench_alloc_data</t>
+          <t>print_array</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -675,13 +816,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>polybench_alloc_data</t>
+          <t>print_array</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -691,13 +841,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>polybench_alloc_data</t>
+          <t>print_array</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -707,13 +866,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>polybench_alloc_data</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -723,13 +891,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>polybench_alloc_data</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
         <v>0</v>
       </c>
     </row>
